--- a/db.xlsx
+++ b/db.xlsx
@@ -826,7 +826,11 @@
           <t>Blackburn Rovers</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -862,7 +866,11 @@
           <t>Burnley</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -934,7 +942,11 @@
           <t>Hull City</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
